--- a/Template Bonifica PC.xlsx
+++ b/Template Bonifica PC.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://logimoda-my.sharepoint.com/personal/flazzaro_efsw_it/Documents/Incident-NEI/Cynet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mstigliano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{67C030A4-684E-4CF7-B135-41621DDAD90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67F59A68-3001-4844-AFB2-1EA6BBD39C18}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F29CBFF-026B-49D3-B642-47E4C8B2F13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8FF7D57-D9A8-4357-8B99-92B6B239E9FC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8FF7D57-D9A8-4357-8B99-92B6B239E9FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">Nome pc </t>
   </si>
@@ -55,25 +56,24 @@
   <si>
     <t>Stato</t>
   </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>COMPROMESSO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-410]General"/>
+    <numFmt numFmtId="164" formatCode="[$-410]General"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -84,21 +84,66 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -111,9 +156,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -126,40 +169,94 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{0A6FB5D8-1271-43D5-84E1-2DDB32EEC169}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -489,24 +586,766 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A2045A-8E77-4ACA-A4D5-D22CD52AE9CA}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D100">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="COMPROMESSO">
+      <formula>NOT(ISERROR(SEARCH("COMPROMESSO",D2)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{35A269ED-FA2F-40C4-99EC-C3CB5CAAE248}">
+          <x14:formula1>
+            <xm:f>Foglio2!$A$1:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D100</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE33318B-7711-4EB2-8F6E-7E6307FDCEC1}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
